--- a/testdata/configurationTST/data.xlsx
+++ b/testdata/configurationTST/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="22080" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="100">
   <si>
     <t>username</t>
   </si>
@@ -113,6 +113,12 @@
     <t>credit_card_2_number</t>
   </si>
   <si>
+    <t>master_installment_card_name</t>
+  </si>
+  <si>
+    <t>master_installment_card_number</t>
+  </si>
+  <si>
     <t>loan_account_number</t>
   </si>
   <si>
@@ -161,58 +167,61 @@
     <t>cards_item_credit_card_number</t>
   </si>
   <si>
+    <t>fee_clean_RSD</t>
+  </si>
+  <si>
+    <t>fee_with_NBSP_RSD</t>
+  </si>
+  <si>
+    <t>auth_personal_account_number</t>
+  </si>
+  <si>
+    <t>auth_personal_account_name</t>
+  </si>
+  <si>
     <t>Osir ANOEV</t>
   </si>
   <si>
     <t>https://uat.dbp.nlb.si/web-retail/login</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>uat</t>
-  </si>
-  <si>
-    <t>9032022325800</t>
+    <t>no</t>
+  </si>
+  <si>
+    <t>tst</t>
+  </si>
+  <si>
+    <t>9012009713957</t>
   </si>
   <si>
     <t>Oročeni depozit</t>
   </si>
   <si>
-    <t>9032009555384</t>
-  </si>
-  <si>
-    <t>9032032968203</t>
-  </si>
-  <si>
-    <t>15. 1. 2016</t>
-  </si>
-  <si>
-    <t>15. 1. 2028</t>
-  </si>
-  <si>
     <t>.</t>
   </si>
   <si>
     <t>Tekući račun</t>
   </si>
   <si>
-    <t>205-9001007790944-88</t>
+    <t>205-9001015596154-64</t>
+  </si>
+  <si>
+    <t>205-9001033140133-36</t>
   </si>
   <si>
     <t>205900100779094488</t>
   </si>
   <si>
-    <t>RS35 2059 0310 0441 9532 81</t>
+    <t>RS35 2059 0310 2395 6964 35</t>
   </si>
   <si>
     <t>Devizni platni račun</t>
   </si>
   <si>
-    <t>RS35 2059 0310 0441 7882 84</t>
-  </si>
-  <si>
-    <t>9011008395360</t>
+    <t>RS35 2059 0310 3438 5640 96</t>
+  </si>
+  <si>
+    <t>9011009711745</t>
   </si>
   <si>
     <t>A vista depozitni račun</t>
@@ -221,24 +230,33 @@
     <t>Naknada za TR</t>
   </si>
   <si>
-    <t>Visa prepaid</t>
-  </si>
-  <si>
-    <t>4431 **** **** 0118</t>
+    <t>Dinacard kreditna</t>
+  </si>
+  <si>
+    <t>6556 **** **** 1687</t>
   </si>
   <si>
     <t>Visa revolving card</t>
   </si>
   <si>
-    <t>4176 **** **** 8476</t>
-  </si>
-  <si>
-    <t>0049019000647</t>
+    <t>4176 **** **** 9367</t>
+  </si>
+  <si>
+    <t>Mastercard Installment Card</t>
+  </si>
+  <si>
+    <t>5309 **** **** 2304</t>
+  </si>
+  <si>
+    <t>0049031090317</t>
   </si>
   <si>
     <t>Gotovinski kredit</t>
   </si>
   <si>
+    <t>0049032668797</t>
+  </si>
+  <si>
     <t>340000003253595464</t>
   </si>
   <si>
@@ -257,115 +275,58 @@
     <t>170-0000000000772-26</t>
   </si>
   <si>
-    <t>OSIR ANOEV</t>
+    <t>BOŽICA ANGELA</t>
+  </si>
+  <si>
+    <t>Visa PayWave - BOŽICA KOLAREVIĆ</t>
+  </si>
+  <si>
+    <t>4381********0511</t>
+  </si>
+  <si>
+    <t>Dina International Credit - BOŽICA KOLAREVIĆ</t>
+  </si>
+  <si>
+    <t>6556********1687</t>
+  </si>
+  <si>
+    <t>15,00 RSD</t>
+  </si>
+  <si>
+    <t>15,00 RSD</t>
+  </si>
+  <si>
+    <t>205-9001006224465-69</t>
+  </si>
+  <si>
+    <t>MILIJAN MILEN</t>
   </si>
   <si>
     <t>Enil ČIĆVI</t>
   </si>
   <si>
-    <t>9032030694661</t>
-  </si>
-  <si>
-    <t>8. 6. 2022</t>
-  </si>
-  <si>
-    <t>8. 6. 2028</t>
-  </si>
-  <si>
-    <t>9031008901983</t>
-  </si>
-  <si>
-    <t>205-9001010537788-94</t>
-  </si>
-  <si>
-    <t>205-9001015647000-10</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0905 7582 96</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0890 1983 32</t>
-  </si>
-  <si>
-    <t>ČIĆVI OLIK</t>
-  </si>
-  <si>
-    <t>ČIĆVI ENIL</t>
-  </si>
-  <si>
     <t>Aor IĆVR</t>
   </si>
   <si>
-    <t>205-9001021348944-31</t>
+    <t>PETKO NOVAK</t>
+  </si>
+  <si>
+    <t>Icer OVIVL</t>
+  </si>
+  <si>
+    <t>205900100417516512</t>
   </si>
   <si>
     <t>205-9001000302715-60</t>
   </si>
   <si>
-    <t>PETKO NOVAK</t>
-  </si>
-  <si>
-    <t>9032031803286</t>
-  </si>
-  <si>
-    <t>9032033386437</t>
-  </si>
-  <si>
-    <t>9011009710234</t>
-  </si>
-  <si>
-    <t>205-9001006224465-69</t>
-  </si>
-  <si>
-    <t>205-9001004175165-12</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0048 9390 60</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 2550 7717 90</t>
-  </si>
-  <si>
-    <t>0049041360495</t>
-  </si>
-  <si>
-    <t>MILIJAN MILEN</t>
-  </si>
-  <si>
-    <t>Icer OVIVL</t>
-  </si>
-  <si>
-    <t>205900100417516512</t>
-  </si>
-  <si>
-    <t>OVIVL OSIR</t>
-  </si>
-  <si>
     <t>Vklaragan OVIT</t>
   </si>
   <si>
-    <t>205-9001004906720-69</t>
-  </si>
-  <si>
     <t>205900100490672069</t>
   </si>
   <si>
-    <t>STANIŠA NIKOLA</t>
-  </si>
-  <si>
     <t>Jail ĆEVGIMILĆ</t>
-  </si>
-  <si>
-    <t>205-9001001626239-86</t>
-  </si>
-  <si>
-    <t>0049018568496</t>
-  </si>
-  <si>
-    <t>Stambeni kredit</t>
-  </si>
-  <si>
-    <t>0049005001233</t>
   </si>
 </sst>
 </file>
@@ -378,7 +339,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,19 +376,6 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -894,137 +842,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1037,6 +985,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1049,18 +1000,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1071,12 +1010,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1398,7 +1331,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AR9"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr defaultColWidth="8.87962962962963" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
@@ -1423,23 +1356,29 @@
     <col min="22" max="22" width="22.8888888888889" customWidth="1"/>
     <col min="23" max="24" width="24.6666666666667" customWidth="1"/>
     <col min="25" max="28" width="33.2222222222222" customWidth="1"/>
-    <col min="29" max="29" width="21.2222222222222" customWidth="1"/>
-    <col min="30" max="30" width="19.4444444444444" customWidth="1"/>
-    <col min="31" max="31" width="22.4444444444444" customWidth="1"/>
+    <col min="29" max="29" width="29.1111111111111" customWidth="1"/>
+    <col min="30" max="30" width="31.5555555555556" customWidth="1"/>
+    <col min="31" max="31" width="21.2222222222222" customWidth="1"/>
     <col min="32" max="32" width="19.4444444444444" customWidth="1"/>
-    <col min="33" max="33" width="23.7777777777778" customWidth="1"/>
-    <col min="34" max="34" width="31.5555555555556" customWidth="1"/>
+    <col min="33" max="33" width="22.4444444444444" customWidth="1"/>
+    <col min="34" max="34" width="19.4444444444444" customWidth="1"/>
     <col min="35" max="35" width="23.7777777777778" customWidth="1"/>
     <col min="36" max="36" width="31.5555555555556" customWidth="1"/>
     <col min="37" max="37" width="23.7777777777778" customWidth="1"/>
     <col min="38" max="38" width="31.5555555555556" customWidth="1"/>
-    <col min="39" max="40" width="22.1111111111111" customWidth="1"/>
-    <col min="41" max="42" width="27.8888888888889" customWidth="1"/>
-    <col min="43" max="43" width="31.7777777777778" customWidth="1"/>
-    <col min="44" max="44" width="27.8888888888889" customWidth="1"/>
+    <col min="39" max="39" width="23.7777777777778" customWidth="1"/>
+    <col min="40" max="40" width="31.5555555555556" customWidth="1"/>
+    <col min="41" max="42" width="22.1111111111111" customWidth="1"/>
+    <col min="43" max="43" width="27.8888888888889" customWidth="1"/>
+    <col min="44" max="44" width="29.7777777777778" customWidth="1"/>
+    <col min="45" max="45" width="42.6666666666667" customWidth="1"/>
+    <col min="46" max="46" width="27.8888888888889" customWidth="1"/>
+    <col min="47" max="47" width="14.4444444444444" customWidth="1"/>
+    <col min="48" max="48" width="20.7777777777778" customWidth="1"/>
+    <col min="49" max="50" width="30.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:44">
+    <row r="1" customFormat="1" spans="1:50">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1536,10 +1475,10 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
@@ -1572,1074 +1511,1239 @@
       <c r="AR1" t="s">
         <v>43</v>
       </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:44">
+    <row r="2" customFormat="1" spans="1:50">
       <c r="A2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:50">
+      <c r="A3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="E3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="G3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="I3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="J3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="O3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="P3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="V2" s="14" t="s">
+      <c r="R3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="T3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="U3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="V3" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="W3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="AA2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB2" s="1" t="s">
+      <c r="X3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="Z3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AB3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AC3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AD3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AE3" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="AK2" s="15" t="s">
+      <c r="AF3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AG3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="AM2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>54</v>
+      <c r="AH3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:44">
-      <c r="A3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:44">
+    <row r="4" customFormat="1" spans="1:50">
       <c r="A4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:50">
+      <c r="A5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI5" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:50">
+      <c r="A6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="K6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW6" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="AX6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:50">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="G7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX7" t="s">
         <v>90</v>
       </c>
-      <c r="R4" s="1" t="s">
+    </row>
+    <row r="8" customFormat="1" spans="1:50">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="H8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="J8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:50">
+      <c r="A9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:44">
-      <c r="A5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="T5" s="1" t="s">
+      <c r="K9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="U5" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="V5" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="W5" s="1" t="s">
+      <c r="R9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC5" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD5" s="1" t="s">
+      <c r="U9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE5" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG5" s="15" t="s">
+      <c r="AB9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AH5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:44">
-      <c r="A6" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="V6" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC6" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE6" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG6" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:44">
-      <c r="A7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="R7" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG7" s="1" t="s">
+      <c r="AD9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX9" t="s">
         <v>90</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN7" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:44">
-      <c r="A8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="R8" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AG8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AN8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:44">
-      <c r="A9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC9" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE9" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>54</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>54</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
